--- a/xls/square_16_tri3_9.xlsx
+++ b/xls/square_16_tri3_9.xlsx
@@ -482,13 +482,13 @@
         <v>486</v>
       </c>
       <c r="I9">
-        <v>2.0506673003291147</v>
+        <v>2.0506669825277757</v>
       </c>
       <c r="J9">
-        <v>-1.0660796892660158</v>
+        <v>-1.0660800329891524</v>
       </c>
       <c r="K9">
-        <v>-0.34369158120579757</v>
+        <v>-0.34369187048559335</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -517,13 +517,13 @@
         <v>600</v>
       </c>
       <c r="I10">
-        <v>-1.8918592968389774</v>
+        <v>-1.8918591705925119</v>
       </c>
       <c r="J10">
-        <v>-1.8534257461345927</v>
+        <v>-1.853425364867128</v>
       </c>
       <c r="K10">
-        <v>-1.1442278277575486</v>
+        <v>-1.1442275701375269</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -552,13 +552,13 @@
         <v>726</v>
       </c>
       <c r="I11">
-        <v>-1.8915148876249006</v>
+        <v>-1.8915137503471349</v>
       </c>
       <c r="J11">
-        <v>-1.9032661417633334</v>
+        <v>-1.9032653425024797</v>
       </c>
       <c r="K11">
-        <v>-1.1543297677753865</v>
+        <v>-1.1543296961643879</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -587,13 +587,13 @@
         <v>864</v>
       </c>
       <c r="I12">
-        <v>-1.887614410807637</v>
+        <v>-1.8876144241271666</v>
       </c>
       <c r="J12">
-        <v>-1.6435148177870893</v>
+        <v>-1.643514858370497</v>
       </c>
       <c r="K12">
-        <v>-0.656466083757104</v>
+        <v>-0.6564661420647095</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -622,13 +622,13 @@
         <v>1014</v>
       </c>
       <c r="I13">
-        <v>-1.7421813373349768</v>
+        <v>-1.742182458619732</v>
       </c>
       <c r="J13">
-        <v>-1.4230884433381608</v>
+        <v>-1.42308869841634</v>
       </c>
       <c r="K13">
-        <v>-0.3995375173018641</v>
+        <v>-0.3995374576625452</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -657,13 +657,13 @@
         <v>1176</v>
       </c>
       <c r="I14">
-        <v>-1.3291446816548549</v>
+        <v>-1.3291446383060368</v>
       </c>
       <c r="J14">
-        <v>-1.0440180310529035</v>
+        <v>-1.044017990141926</v>
       </c>
       <c r="K14">
-        <v>-0.022719198134807824</v>
+        <v>-0.022719208567161454</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -692,13 +692,13 @@
         <v>1350</v>
       </c>
       <c r="I15">
-        <v>-0.8562484709529379</v>
+        <v>-0.8562486028349867</v>
       </c>
       <c r="J15">
-        <v>-0.6470707395290938</v>
+        <v>-0.6470707875165466</v>
       </c>
       <c r="K15">
-        <v>0.3512417312197032</v>
+        <v>0.3512417222700448</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -727,13 +727,13 @@
         <v>1536</v>
       </c>
       <c r="I16">
-        <v>-1.515777653581837</v>
+        <v>-1.5157776374112708</v>
       </c>
       <c r="J16">
-        <v>-1.2308132286638294</v>
+        <v>-1.230813202687646</v>
       </c>
       <c r="K16">
-        <v>-0.1860128743761208</v>
+        <v>-0.1860128687664807</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -762,13 +762,13 @@
         <v>1734</v>
       </c>
       <c r="I17">
-        <v>-0.018440918293317964</v>
+        <v>-0.01844091520431105</v>
       </c>
       <c r="J17">
-        <v>-0.01654650036152495</v>
+        <v>-0.016546498644532646</v>
       </c>
       <c r="K17">
-        <v>2.0531886781327406</v>
+        <v>2.0531886293467667</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -797,13 +797,13 @@
         <v>1944</v>
       </c>
       <c r="I18">
-        <v>-0.003907567557529824</v>
+        <v>-0.003907567575336271</v>
       </c>
       <c r="J18">
-        <v>-0.004699283489682265</v>
+        <v>-0.0046992835070868225</v>
       </c>
       <c r="K18">
-        <v>3.2842936466021833</v>
+        <v>3.284293647709039</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -832,13 +832,13 @@
         <v>2166</v>
       </c>
       <c r="I19">
-        <v>-0.00018959767988194245</v>
+        <v>-0.00018959767988792388</v>
       </c>
       <c r="J19">
-        <v>-0.00012737885266116665</v>
+        <v>-0.00012737885266594147</v>
       </c>
       <c r="K19">
-        <v>2.3357249915213227</v>
+        <v>2.3357249913060834</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -867,13 +867,13 @@
         <v>2400</v>
       </c>
       <c r="I20">
-        <v>-1.8927739452386204e-5</v>
+        <v>-1.8927739457786673e-5</v>
       </c>
       <c r="J20">
-        <v>-1.3468288473947828e-5</v>
+        <v>-1.34682884768409e-5</v>
       </c>
       <c r="K20">
-        <v>1.9205511272172495</v>
+        <v>1.9205511272374807</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -905,10 +905,10 @@
         <v>5.877224077863167e-6</v>
       </c>
       <c r="J21">
-        <v>1.275229537545078e-6</v>
+        <v>1.275229537737943e-6</v>
       </c>
       <c r="K21">
-        <v>1.7360538731309785</v>
+        <v>1.7360538731782562</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -937,13 +937,13 @@
         <v>2904</v>
       </c>
       <c r="I22">
-        <v>5.129481068399187e-6</v>
+        <v>5.129481068495619e-6</v>
       </c>
       <c r="J22">
-        <v>1.1706868974550834e-6</v>
+        <v>1.170686897358651e-6</v>
       </c>
       <c r="K22">
-        <v>1.709774664532132</v>
+        <v>1.709774664781173</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -978,7 +978,7 @@
         <v>-1.1949503801126558e-6</v>
       </c>
       <c r="K23">
-        <v>1.63103013953403</v>
+        <v>1.6310301397702938</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1007,13 +1007,13 @@
         <v>3456</v>
       </c>
       <c r="I24">
-        <v>-1.8143362490253295e-6</v>
+        <v>-1.8143362489288965e-6</v>
       </c>
       <c r="J24">
-        <v>-1.6255330387121274e-6</v>
+        <v>-1.6255330389049936e-6</v>
       </c>
       <c r="K24">
-        <v>1.585005211965963</v>
+        <v>1.5850052117653495</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1042,13 +1042,13 @@
         <v>3750</v>
       </c>
       <c r="I25">
-        <v>-1.3879094659489876e-6</v>
+        <v>-1.3879094659007708e-6</v>
       </c>
       <c r="J25">
-        <v>-8.678227132582522e-7</v>
+        <v>-8.678227131618193e-7</v>
       </c>
       <c r="K25">
-        <v>1.2871771856170653</v>
+        <v>1.2871771855068106</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1077,13 +1077,13 @@
         <v>4056</v>
       </c>
       <c r="I26">
-        <v>7.038290716407866e-8</v>
+        <v>7.038290745337684e-8</v>
       </c>
       <c r="J26">
-        <v>-3.4964849806540316e-8</v>
+        <v>-3.4964849854756694e-8</v>
       </c>
       <c r="K26">
-        <v>1.0423788756922017</v>
+        <v>1.0423788757386816</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1112,13 +1112,13 @@
         <v>4374</v>
       </c>
       <c r="I27">
-        <v>7.62768821054585e-8</v>
+        <v>7.627688200902577e-8</v>
       </c>
       <c r="J27">
-        <v>-3.63145793901632e-8</v>
+        <v>-3.631457924551407e-8</v>
       </c>
       <c r="K27">
-        <v>1.0482439695889156</v>
+        <v>1.048243969794356</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1147,13 +1147,13 @@
         <v>4704</v>
       </c>
       <c r="I28">
-        <v>-3.723584918296611e-8</v>
+        <v>-3.723584937583162e-8</v>
       </c>
       <c r="J28">
         <v>-7.844616238592985e-8</v>
       </c>
       <c r="K28">
-        <v>1.0017391564140752</v>
+        <v>1.001739156477176</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1182,13 +1182,13 @@
         <v>5046</v>
       </c>
       <c r="I29">
-        <v>-5.317641134920966e-8</v>
+        <v>-5.317641139742605e-8</v>
       </c>
       <c r="J29">
         <v>-8.218602383717696e-8</v>
       </c>
       <c r="K29">
-        <v>0.9835826237615953</v>
+        <v>0.9835826237986498</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1217,13 +1217,13 @@
         <v>5400</v>
       </c>
       <c r="I30">
-        <v>-5.6137622025593155e-8</v>
+        <v>-5.6137621880944015e-8</v>
       </c>
       <c r="J30">
-        <v>-8.77317877071294e-8</v>
+        <v>-8.773178780356217e-8</v>
       </c>
       <c r="K30">
-        <v>0.9964541789195269</v>
+        <v>0.9964541789942479</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1258,7 +1258,7 @@
         <v>-2.0608929519468624e-8</v>
       </c>
       <c r="K31">
-        <v>1.003820701526463</v>
+        <v>1.0038207016850833</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1287,13 +1287,13 @@
         <v>6144</v>
       </c>
       <c r="I32">
-        <v>2.5296349131461008e-8</v>
+        <v>2.5296349035028266e-8</v>
       </c>
       <c r="J32">
-        <v>-4.535276584280389e-8</v>
+        <v>-4.535276598745302e-8</v>
       </c>
       <c r="K32">
-        <v>0.9914092251383114</v>
+        <v>0.9914092249251418</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_16_tri3_9.xlsx
+++ b/xls/square_16_tri3_9.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>100</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7">
+        <v>289</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7">
+        <v>64</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>294</v>
+      </c>
+      <c r="I7">
+        <v>22.84801070376746</v>
+      </c>
+      <c r="J7">
+        <v>8.896661497256709</v>
+      </c>
+      <c r="K7">
+        <v>8.96459651566552</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <v>100</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8">
+        <v>289</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8">
+        <v>81</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8">
+        <v>384</v>
+      </c>
+      <c r="I8">
+        <v>4.8642887881037895</v>
+      </c>
+      <c r="J8">
+        <v>1.2075503766320814</v>
+      </c>
+      <c r="K8">
+        <v>1.696928550449584</v>
+      </c>
+    </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
         <v>11</v>
